--- a/NOC_MTTR_Report.xlsx
+++ b/NOC_MTTR_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tejasandeep_c\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adidasgroup.sharepoint.com/sites/connect/Shared Documents/013 Operations/Operational KPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{B7EE8313-4F3B-4583-ADA7-DDA17030689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95615CA4-B73F-46E0-BF62-4C0014CCE017}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{B7EE8313-4F3B-4583-ADA7-DDA17030689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B75AE4FB-856C-4C56-BC12-403AA01BBDEA}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11443" firstSheet="1" activeTab="1" xr2:uid="{F44E7462-D26D-4CE0-8E30-F9E3BFC2560B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F44E7462-D26D-4CE0-8E30-F9E3BFC2560B}"/>
   </bookViews>
   <sheets>
     <sheet name="NOC_MTTR" sheetId="1" r:id="rId1"/>
@@ -217,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,17 +669,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613A53DE-2B0F-44FD-9DA5-E08D04CBABE2}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -697,7 +697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45839</v>
       </c>
@@ -717,7 +717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46235</v>
       </c>
@@ -737,7 +737,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46266</v>
       </c>
@@ -757,7 +757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45931</v>
       </c>
@@ -777,7 +777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45962</v>
       </c>
@@ -797,7 +797,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45992</v>
       </c>
@@ -817,7 +817,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46023</v>
       </c>
@@ -837,7 +837,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46054</v>
       </c>
@@ -857,7 +857,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46082</v>
       </c>
@@ -877,24 +877,52 @@
         <v>47</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46235</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539BF5F2-EF88-4288-8ABD-042247B5A4B3}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,57 +939,57 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45839</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46235</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46266</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45931</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45962</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46054</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>46113</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46143</v>
       </c>
@@ -981,7 +1009,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46174</v>
       </c>
@@ -1001,38 +1029,41 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18">
+    <row r="14" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="D14" s="4"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" ht="18">
+    <row r="15" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="D15" s="4"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:7" ht="18">
+    <row r="16" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="2:5" ht="18">
+    <row r="17" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B17" s="6"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="2:5" ht="18">
+    <row r="18" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B18" s="6"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="2:5" ht="18">
+    <row r="19" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B19" s="6"/>
     </row>
-    <row r="20" spans="2:5" ht="18">
+    <row r="20" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B20" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
@@ -1327,15 +1358,47 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E3F269-C870-4D23-A66D-7F6832BF1875}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E3F269-C870-4D23-A66D-7F6832BF1875}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="dc4dcb21-90d3-4695-adc8-464bc3ea11a9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB3424C-A238-4E06-BFA9-64918DF59714}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB3424C-A238-4E06-BFA9-64918DF59714}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73"/>
+    <ds:schemaRef ds:uri="dc4dcb21-90d3-4695-adc8-464bc3ea11a9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD6048B-2CEB-4BEA-8F88-1C042992C094}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD6048B-2CEB-4BEA-8F88-1C042992C094}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
